--- a/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 15,8</t>
+          <t>8,5; 15,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 13,55</t>
+          <t>6,8; 13,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 16,99</t>
+          <t>9,07; 16,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 12,6</t>
+          <t>3,14; 12,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,42; 24,03</t>
+          <t>11,96; 23,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 18,32</t>
+          <t>8,7; 18,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,88; 24,29</t>
+          <t>12,11; 24,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 21,54</t>
+          <t>4,88; 21,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,38; 18,25</t>
+          <t>11,32; 18,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 15,78</t>
+          <t>8,91; 15,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 12,35</t>
+          <t>5,92; 12,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 29,06</t>
+          <t>2,23; 27,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,15; 49,27</t>
+          <t>27,97; 50,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,96; 34,97</t>
+          <t>18,23; 34,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,2; 26,89</t>
+          <t>12,07; 26,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 107,84</t>
+          <t>6,26; 96,07</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 19,18</t>
+          <t>6,25; 18,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 13,31</t>
+          <t>-0,11; 13,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 13,67</t>
+          <t>2,03; 14,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 6,75</t>
+          <t>-3,35; 7,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,84; 52,32</t>
+          <t>14,65; 52,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 30,18</t>
+          <t>0,06; 32,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 36,39</t>
+          <t>4,39; 37,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 21,89</t>
+          <t>-9,54; 23,02</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,35; 18,09</t>
+          <t>13,46; 18,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,52; 16,07</t>
+          <t>11,32; 15,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,91</t>
+          <t>9,04; 14,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 22,56</t>
+          <t>4,48; 22,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,26; 38,54</t>
+          <t>27,03; 38,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,03; 29,69</t>
+          <t>19,84; 29,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 27,57</t>
+          <t>16,86; 27,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 70,53</t>
+          <t>10,67; 71,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>11,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 15,75</t>
+          <t>8,57; 15,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,5</t>
+          <t>7,23; 13,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 16,85</t>
+          <t>9,41; 17,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 12,73</t>
+          <t>6,34; 15,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 23,83</t>
+          <t>12,1; 23,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 18,25</t>
+          <t>9,14; 17,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 24,08</t>
+          <t>12,54; 24,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 21,58</t>
+          <t>10,28; 29,06</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,09</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 18,41</t>
+          <t>11,23; 18,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 15,56</t>
+          <t>9,19; 15,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,3</t>
+          <t>5,62; 12,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 27,1</t>
+          <t>1,46; 7,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,97; 50,72</t>
+          <t>27,9; 49,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,23; 34,28</t>
+          <t>18,87; 34,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,07; 26,8</t>
+          <t>11,3; 26,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 96,07</t>
+          <t>3,82; 21,42</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 18,86</t>
+          <t>6,47; 19,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 13,67</t>
+          <t>-0,88; 13,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 14,26</t>
+          <t>1,1; 13,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 7,07</t>
+          <t>-2,57; 6,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,65; 52,01</t>
+          <t>15,38; 52,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 32,25</t>
+          <t>-1,68; 29,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 37,07</t>
+          <t>2,52; 35,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 23,02</t>
+          <t>-7,16; 23,12</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,45</t>
+          <t>6,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 18,0</t>
+          <t>13,23; 18,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 15,86</t>
+          <t>11,19; 16,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 14,19</t>
+          <t>9,02; 13,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 22,71</t>
+          <t>4,37; 8,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,03; 38,58</t>
+          <t>26,86; 38,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,84; 29,26</t>
+          <t>19,69; 29,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,86; 27,84</t>
+          <t>16,75; 27,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 71,96</t>
+          <t>10,56; 22,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
